--- a/Dataset_1/4_Integration_results/Stats_table_region.xlsx
+++ b/Dataset_1/4_Integration_results/Stats_table_region.xlsx
@@ -12,7 +12,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t xml:space="preserve">metric</t>
+  </si>
   <si>
     <t xml:space="preserve">M1</t>
   </si>
@@ -29,67 +32,40 @@
     <t xml:space="preserve">M5</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.727677338354276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993061875709262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NaN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.690969027241724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895527859237537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0392811482015576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0717173671228901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997542685235945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364973262032086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238951020050345</t>
+    <t xml:space="preserve">Perc ∩ prom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign prom (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc ∩ exon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign exon (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc ∩ intron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign intron (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc ∩ interg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign interg (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc ∩ 5'UTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign 5'UTR (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc ∩ 3'UTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign 3'UTR (padj)</t>
   </si>
 </sst>
 </file>
@@ -434,209 +410,228 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="B2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="B6" t="n">
+        <v>49</v>
+      </c>
+      <c r="C6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D6"/>
+      <c r="E6" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.471998279119032</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.471998279119032</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.471998279119032</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="B12" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
